--- a/data/trans_orig/P24C-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P24C-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que deje de fumar en 2007</t>
+          <t>Población según si su médico le ha aconsejado que deje de fumar en 2007 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>96760</t>
+          <t>94615</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>131399</t>
+          <t>132132</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42659</t>
+          <t>41915</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65407</t>
+          <t>66725</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>146161</t>
+          <t>146775</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>189976</t>
+          <t>189986</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>120323</t>
+          <t>120985</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>157077</t>
+          <t>159180</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70791</t>
+          <t>71319</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>97254</t>
+          <t>96963</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>200123</t>
+          <t>201106</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>247964</t>
+          <t>248317</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,12%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>103867</t>
+          <t>102593</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>138895</t>
+          <t>138531</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27774</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48941</t>
+          <t>50269</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>137137</t>
+          <t>138063</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>179996</t>
+          <t>182733</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>360818</t>
+          <t>363670</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423004</t>
+          <t>422879</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>215109</t>
+          <t>214080</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>261655</t>
+          <t>260454</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>585554</t>
+          <t>594891</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>663273</t>
+          <t>666906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,9%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>279917</t>
+          <t>278151</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>335926</t>
+          <t>335716</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>189880</t>
+          <t>189490</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>234744</t>
+          <t>232096</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>484215</t>
+          <t>480352</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>555425</t>
+          <t>552311</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,5%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>98250</t>
+          <t>98280</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>138787</t>
+          <t>138766</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79699</t>
+          <t>80414</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>113813</t>
+          <t>116584</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>189083</t>
+          <t>188913</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>244818</t>
+          <t>243620</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>82201</t>
+          <t>80450</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>110627</t>
+          <t>110998</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43707</t>
+          <t>43913</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66495</t>
+          <t>67733</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>131762</t>
+          <t>132120</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>167901</t>
+          <t>169184</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>51,02%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50770</t>
+          <t>49929</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>79280</t>
+          <t>77422</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40328</t>
+          <t>41535</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62929</t>
+          <t>63098</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>99090</t>
+          <t>97891</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>136028</t>
+          <t>133394</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>40,23%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23331</t>
+          <t>23523</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>45143</t>
+          <t>46850</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22878</t>
+          <t>22221</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42979</t>
+          <t>42516</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>52889</t>
+          <t>51349</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>83751</t>
+          <t>81510</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>563792</t>
+          <t>563606</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>639292</t>
+          <t>636307</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>317656</t>
+          <t>318528</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>374861</t>
+          <t>378223</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>898567</t>
+          <t>900423</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>996624</t>
+          <t>995130</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,31%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>472035</t>
+          <t>474465</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>546227</t>
+          <t>545618</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>322346</t>
+          <t>319714</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>378871</t>
+          <t>375955</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>813423</t>
+          <t>810310</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>907251</t>
+          <t>905506</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,32%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>243911</t>
+          <t>243775</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>304309</t>
+          <t>305297</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>145970</t>
+          <t>142891</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>190037</t>
+          <t>189219</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>396724</t>
+          <t>405834</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>475745</t>
+          <t>484202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que deje de fumar en 2012</t>
+          <t>Población según si su médico le ha aconsejado que deje de fumar en 2012 (tasa de respuesta: 99,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27530</t>
+          <t>26982</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50383</t>
+          <t>49708</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>8346</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23495</t>
+          <t>23494</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40190</t>
+          <t>39062</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67003</t>
+          <t>66138</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>117079</t>
+          <t>116913</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>153845</t>
+          <t>155336</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93776</t>
+          <t>93059</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>121840</t>
+          <t>122281</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>219595</t>
+          <t>219626</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>265974</t>
+          <t>266956</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,99%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>141868</t>
+          <t>143712</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>179997</t>
+          <t>181104</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>64947</t>
+          <t>63974</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>92257</t>
+          <t>91973</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>216607</t>
+          <t>216252</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>264185</t>
+          <t>264878</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,6%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>137194</t>
+          <t>139411</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>186479</t>
+          <t>185535</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>73844</t>
+          <t>75003</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>110455</t>
+          <t>112500</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>221300</t>
+          <t>224671</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>282671</t>
+          <t>284565</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,21%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>375808</t>
+          <t>377194</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>438808</t>
+          <t>440000</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>282186</t>
+          <t>282339</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>334953</t>
+          <t>333718</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>674059</t>
+          <t>676774</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>752514</t>
+          <t>758076</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>51,18%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>247169</t>
+          <t>245579</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>303297</t>
+          <t>306819</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>213839</t>
+          <t>211007</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>263072</t>
+          <t>261040</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>473964</t>
+          <t>476366</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>552294</t>
+          <t>550942</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,2%</t>
         </is>
       </c>
     </row>
@@ -3699,12 +3699,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24474</t>
+          <t>24615</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48125</t>
+          <t>47268</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23576</t>
+          <t>22822</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45172</t>
+          <t>45077</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>55298</t>
+          <t>53618</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>88368</t>
+          <t>84846</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>28,2%</t>
         </is>
       </c>
     </row>
@@ -3812,12 +3812,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67491</t>
+          <t>67259</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95364</t>
+          <t>94358</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47090</t>
+          <t>46883</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72285</t>
+          <t>72117</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120906</t>
+          <t>123023</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>157576</t>
+          <t>159292</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,95%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33536</t>
+          <t>34040</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>60508</t>
+          <t>58683</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35995</t>
+          <t>35641</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59148</t>
+          <t>59059</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>77114</t>
+          <t>78114</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>113397</t>
+          <t>111676</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,12%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>207423</t>
+          <t>208050</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>263705</t>
+          <t>261339</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>117604</t>
+          <t>117588</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>163261</t>
+          <t>162324</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>338488</t>
+          <t>340068</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>412290</t>
+          <t>412725</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -4268,12 +4268,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>585939</t>
+          <t>585342</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>664541</t>
+          <t>661449</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>446884</t>
+          <t>442571</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>508856</t>
+          <t>508273</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1046635</t>
+          <t>1050209</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1145222</t>
+          <t>1147926</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,56%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>447610</t>
+          <t>448678</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>521210</t>
+          <t>520580</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>327527</t>
+          <t>326717</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>389445</t>
+          <t>391436</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>795871</t>
+          <t>796742</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>892113</t>
+          <t>891237</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,48%</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que deje de fumar en 2016</t>
+          <t>Población según si su médico le ha aconsejado que deje de fumar en 2016 (tasa de respuesta: 97,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13334</t>
+          <t>13739</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31163</t>
+          <t>32468</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3895</t>
+          <t>3959</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15360</t>
+          <t>15587</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21122</t>
+          <t>20242</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42427</t>
+          <t>41560</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -4955,12 +4955,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92470</t>
+          <t>94166</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>122067</t>
+          <t>121933</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46406</t>
+          <t>46271</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68605</t>
+          <t>69825</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>146963</t>
+          <t>147090</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>182104</t>
+          <t>184951</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>52,4%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>79987</t>
+          <t>78672</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>108355</t>
+          <t>106667</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>54021</t>
+          <t>52724</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>76785</t>
+          <t>76699</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>140629</t>
+          <t>138923</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>175496</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>49,72%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>102130</t>
+          <t>100734</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>145158</t>
+          <t>142486</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>76386</t>
+          <t>77694</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>114360</t>
+          <t>112813</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>186919</t>
+          <t>191209</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>242985</t>
+          <t>245191</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,01%</t>
         </is>
       </c>
     </row>
@@ -5411,12 +5411,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>361417</t>
+          <t>362159</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>416596</t>
+          <t>420146</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>283317</t>
+          <t>280576</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>332389</t>
+          <t>333130</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>657960</t>
+          <t>655637</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>734901</t>
+          <t>736444</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>51,1%</t>
         </is>
       </c>
     </row>
@@ -5524,12 +5524,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>258623</t>
+          <t>253958</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>314523</t>
+          <t>310276</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>217292</t>
+          <t>222027</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>268369</t>
+          <t>273471</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>488478</t>
+          <t>489858</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>562745</t>
+          <t>566650</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,32%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23311</t>
+          <t>23740</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46060</t>
+          <t>45598</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13647</t>
+          <t>13369</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30054</t>
+          <t>29783</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>42110</t>
+          <t>41728</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>69609</t>
+          <t>68278</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>26,7%</t>
         </is>
       </c>
     </row>
@@ -5867,12 +5867,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52937</t>
+          <t>51484</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77546</t>
+          <t>76741</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47600</t>
+          <t>47473</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69243</t>
+          <t>70446</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>106832</t>
+          <t>105589</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>139352</t>
+          <t>139330</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,49%</t>
         </is>
       </c>
     </row>
@@ -5980,12 +5980,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28514</t>
+          <t>28295</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>50419</t>
+          <t>49236</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31294</t>
+          <t>29907</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51436</t>
+          <t>51517</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>64701</t>
+          <t>63637</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>95125</t>
+          <t>94266</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>36,87%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>153004</t>
+          <t>151286</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>205219</t>
+          <t>204099</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>105075</t>
+          <t>102812</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>146787</t>
+          <t>145465</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>269599</t>
+          <t>269269</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>333452</t>
+          <t>333308</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -6323,12 +6323,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>523915</t>
+          <t>528667</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>596332</t>
+          <t>595936</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>391396</t>
+          <t>392002</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>451956</t>
+          <t>453463</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>938033</t>
+          <t>938680</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1026793</t>
+          <t>1034589</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>50,47%</t>
         </is>
       </c>
     </row>
@@ -6436,12 +6436,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>381909</t>
+          <t>381107</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>450753</t>
+          <t>448600</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6451,12 +6451,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>321823</t>
+          <t>320881</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>379967</t>
+          <t>381031</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>724382</t>
+          <t>716483</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>809966</t>
+          <t>810067</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,52%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P24C-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P24C-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>94615</t>
+          <t>94887</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>132132</t>
+          <t>130927</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41915</t>
+          <t>42834</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66725</t>
+          <t>67746</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>146775</t>
+          <t>146808</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>189986</t>
+          <t>190526</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,62%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>120985</t>
+          <t>122201</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>159180</t>
+          <t>159220</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>71319</t>
+          <t>70702</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>96963</t>
+          <t>97566</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>201106</t>
+          <t>201001</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>248317</t>
+          <t>245331</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>44,58%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>102593</t>
+          <t>103483</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>138531</t>
+          <t>140427</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>28467</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>50269</t>
+          <t>50258</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>138063</t>
+          <t>139259</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>182733</t>
+          <t>183231</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,29%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>363670</t>
+          <t>364639</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>422879</t>
+          <t>423038</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>214080</t>
+          <t>214090</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>260454</t>
+          <t>261635</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>594891</t>
+          <t>595555</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>666906</t>
+          <t>667183</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,92%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>278151</t>
+          <t>278928</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>335716</t>
+          <t>334907</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>189490</t>
+          <t>190210</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>232096</t>
+          <t>237640</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>480352</t>
+          <t>484828</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>552311</t>
+          <t>557443</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,88%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>98280</t>
+          <t>99120</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>138766</t>
+          <t>139875</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80414</t>
+          <t>79119</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>116584</t>
+          <t>116785</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>188913</t>
+          <t>187864</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>243620</t>
+          <t>242099</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>80450</t>
+          <t>80318</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>110998</t>
+          <t>109171</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43913</t>
+          <t>43499</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67733</t>
+          <t>67227</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>132120</t>
+          <t>131144</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>169184</t>
+          <t>167322</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,46%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49929</t>
+          <t>50511</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77422</t>
+          <t>78183</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41535</t>
+          <t>40941</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63098</t>
+          <t>63184</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97891</t>
+          <t>97964</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>133394</t>
+          <t>132486</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>39,95%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23523</t>
+          <t>23824</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>46850</t>
+          <t>46688</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22221</t>
+          <t>22225</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42516</t>
+          <t>42618</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>51349</t>
+          <t>52407</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>81510</t>
+          <t>82938</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>25,01%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>563606</t>
+          <t>565477</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>636307</t>
+          <t>633093</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>318528</t>
+          <t>319953</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>378223</t>
+          <t>377136</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>900423</t>
+          <t>899861</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>995130</t>
+          <t>994652</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,29%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>474465</t>
+          <t>472753</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>545618</t>
+          <t>546653</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>319714</t>
+          <t>317181</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>375955</t>
+          <t>374681</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>810310</t>
+          <t>810633</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>905506</t>
+          <t>906603</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,37%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>243775</t>
+          <t>244946</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>305297</t>
+          <t>302760</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>142891</t>
+          <t>144247</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>189219</t>
+          <t>190601</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>405834</t>
+          <t>402578</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>484202</t>
+          <t>480266</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26982</t>
+          <t>26962</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49708</t>
+          <t>49078</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8346</t>
+          <t>8188</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23494</t>
+          <t>23124</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39062</t>
+          <t>39897</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66138</t>
+          <t>66739</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>116913</t>
+          <t>115609</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>155336</t>
+          <t>153520</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93059</t>
+          <t>92734</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>122281</t>
+          <t>121512</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>219626</t>
+          <t>220661</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>266956</t>
+          <t>267656</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,12%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>143712</t>
+          <t>143923</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>181104</t>
+          <t>182170</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>63974</t>
+          <t>64406</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>91973</t>
+          <t>92646</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>216252</t>
+          <t>213358</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>264878</t>
+          <t>259498</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>48,59%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>139411</t>
+          <t>138893</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>185535</t>
+          <t>186709</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>75003</t>
+          <t>74140</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>112500</t>
+          <t>110075</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>224671</t>
+          <t>226010</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>284565</t>
+          <t>284319</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,2%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>377194</t>
+          <t>375053</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>440000</t>
+          <t>443385</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>282339</t>
+          <t>279853</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>333718</t>
+          <t>332839</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>676774</t>
+          <t>677614</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>758076</t>
+          <t>754459</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>50,94%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>245579</t>
+          <t>246640</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>306819</t>
+          <t>305339</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>211007</t>
+          <t>213522</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>261040</t>
+          <t>264250</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>476366</t>
+          <t>477299</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>550942</t>
+          <t>555347</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,5%</t>
         </is>
       </c>
     </row>
@@ -3699,12 +3699,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24615</t>
+          <t>24892</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47268</t>
+          <t>47645</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22822</t>
+          <t>22881</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45077</t>
+          <t>43746</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>53618</t>
+          <t>53171</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>84846</t>
+          <t>86024</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,59%</t>
         </is>
       </c>
     </row>
@@ -3812,12 +3812,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67259</t>
+          <t>66364</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94358</t>
+          <t>94823</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46883</t>
+          <t>47329</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72117</t>
+          <t>71624</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>123023</t>
+          <t>120747</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>159292</t>
+          <t>157939</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>52,5%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34040</t>
+          <t>34402</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58683</t>
+          <t>58761</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35641</t>
+          <t>37125</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59059</t>
+          <t>60361</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>78114</t>
+          <t>75436</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>111676</t>
+          <t>111450</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,04%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>208050</t>
+          <t>208704</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>261339</t>
+          <t>264763</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>117588</t>
+          <t>117199</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>162324</t>
+          <t>162056</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>340068</t>
+          <t>335188</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>412725</t>
+          <t>411884</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -4268,12 +4268,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>585342</t>
+          <t>580466</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>661449</t>
+          <t>659120</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>442571</t>
+          <t>445468</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>508273</t>
+          <t>509000</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1050209</t>
+          <t>1049921</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1147926</t>
+          <t>1151442</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,72%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>448678</t>
+          <t>448907</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>520580</t>
+          <t>525199</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>326717</t>
+          <t>331626</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>391436</t>
+          <t>392608</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>796742</t>
+          <t>796063</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>891237</t>
+          <t>893265</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,57%</t>
         </is>
       </c>
     </row>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13739</t>
+          <t>13657</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32468</t>
+          <t>31220</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3959</t>
+          <t>4341</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15587</t>
+          <t>15886</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20242</t>
+          <t>21009</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41560</t>
+          <t>41723</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -4955,12 +4955,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94166</t>
+          <t>91603</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>121933</t>
+          <t>121555</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46271</t>
+          <t>46082</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69825</t>
+          <t>69441</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>147090</t>
+          <t>145584</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>184951</t>
+          <t>184356</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,23%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>78672</t>
+          <t>78652</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>106667</t>
+          <t>107927</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>52724</t>
+          <t>52481</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>76699</t>
+          <t>76892</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>138923</t>
+          <t>138683</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>175496</t>
+          <t>176634</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>50,04%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>100734</t>
+          <t>101608</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>142486</t>
+          <t>144051</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>77694</t>
+          <t>76417</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>112813</t>
+          <t>112675</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>191209</t>
+          <t>188653</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>245191</t>
+          <t>241953</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,79%</t>
         </is>
       </c>
     </row>
@@ -5411,12 +5411,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>362159</t>
+          <t>358361</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>420146</t>
+          <t>417664</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>280576</t>
+          <t>283624</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>333130</t>
+          <t>334667</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>655637</t>
+          <t>662637</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>736444</t>
+          <t>739742</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>51,33%</t>
         </is>
       </c>
     </row>
@@ -5524,12 +5524,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>253958</t>
+          <t>256126</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>310276</t>
+          <t>315804</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>222027</t>
+          <t>218559</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>273471</t>
+          <t>267506</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>489858</t>
+          <t>490716</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>566650</t>
+          <t>564856</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,2%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23740</t>
+          <t>23330</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>45598</t>
+          <t>45316</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13369</t>
+          <t>13814</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29783</t>
+          <t>29825</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>41728</t>
+          <t>41454</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>68278</t>
+          <t>68130</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,65%</t>
         </is>
       </c>
     </row>
@@ -5867,12 +5867,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51484</t>
+          <t>52085</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76741</t>
+          <t>76628</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47473</t>
+          <t>47888</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70446</t>
+          <t>68892</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>105589</t>
+          <t>105628</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>139330</t>
+          <t>139273</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,47%</t>
         </is>
       </c>
     </row>
@@ -5980,12 +5980,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28295</t>
+          <t>27784</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49236</t>
+          <t>49270</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29907</t>
+          <t>30300</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51517</t>
+          <t>51170</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>63637</t>
+          <t>63258</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>94266</t>
+          <t>95689</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>37,43%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>151286</t>
+          <t>150577</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>204099</t>
+          <t>202341</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>102812</t>
+          <t>102499</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>145465</t>
+          <t>142993</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>269269</t>
+          <t>269479</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>333308</t>
+          <t>333790</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,28%</t>
         </is>
       </c>
     </row>
@@ -6323,12 +6323,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>528667</t>
+          <t>526600</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>595936</t>
+          <t>598540</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>392002</t>
+          <t>394606</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>453463</t>
+          <t>454064</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>938680</t>
+          <t>936412</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1034589</t>
+          <t>1031184</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,31%</t>
         </is>
       </c>
     </row>
@@ -6436,12 +6436,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>381107</t>
+          <t>383035</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>448600</t>
+          <t>452052</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6451,12 +6451,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>320881</t>
+          <t>323376</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>381031</t>
+          <t>380671</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>716483</t>
+          <t>720298</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>810067</t>
+          <t>811911</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,61%</t>
         </is>
       </c>
     </row>
